--- a/data/trans_orig/KP10in_T-Edad-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Edad-trans_orig.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por tutor (escala)</t>
+          <t>KIDSCREEN percibido por tutor (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>65,18</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>65,6</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>65,41</t>
         </is>
       </c>
     </row>
@@ -571,24 +571,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63,09; 67,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63,44; 67,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63,91; 66,94</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>12-15</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>65,44</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63,92</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64,64</t>
         </is>
       </c>
     </row>
@@ -621,24 +621,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>61,53; 67,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>61,35; 65,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,04; 66,1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8-11</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>65,18</t>
+          <t>65,35</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>65,6</t>
+          <t>64,57</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65,41</t>
+          <t>64,93</t>
         </is>
       </c>
     </row>
@@ -671,135 +671,33 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,94; 67,09</t>
+          <t>62,67; 66,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63,6; 67,68</t>
+          <t>62,74; 66,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,95; 67,06</t>
+          <t>63,26; 66,08</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>65,44</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>63,92</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>64,64</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>60,83; 67,67</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>61,31; 65,75</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>62,28; 66,18</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>65,35</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>64,57</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>64,93</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>62,53; 66,91</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>62,82; 66,11</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>63,48; 66,02</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="4">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A4:A5"/>
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/KP10in_T-Edad-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Edad-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por tutor (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN percibido por adulto (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>63,09; 67,23</t>
+          <t>63,31; 67,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63,44; 67,62</t>
+          <t>63,58; 67,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,91; 66,94</t>
+          <t>64,02; 66,99</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,53; 67,81</t>
+          <t>61,07; 67,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,35; 65,88</t>
+          <t>61,38; 65,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,04; 66,1</t>
+          <t>62,62; 66,21</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,67; 66,91</t>
+          <t>62,34; 66,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,74; 66,11</t>
+          <t>62,85; 66,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,26; 66,08</t>
+          <t>63,3; 66,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KP10in_T-Edad-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Edad-trans_orig.xlsx
@@ -489,18 +489,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por adulto (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN percibido por adulto/a (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>65,18</t>
+          <t>65,71</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>65,6</t>
+          <t>65,37</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65,41</t>
+          <t>65,56</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>63,31; 67,25</t>
+          <t>63,79; 67,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63,58; 67,71</t>
+          <t>63,01; 67,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,02; 66,99</t>
+          <t>64,1; 67,19</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>65,44</t>
+          <t>64,44</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63,92</t>
+          <t>66,82</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64,64</t>
+          <t>65,54</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,07; 67,61</t>
+          <t>62,63; 66,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,38; 65,76</t>
+          <t>65,07; 68,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,62; 66,21</t>
+          <t>64,39; 66,76</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>65,35</t>
+          <t>64,93</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>64,57</t>
+          <t>66,28</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64,93</t>
+          <t>65,55</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,34; 66,79</t>
+          <t>63,64; 66,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,85; 66,07</t>
+          <t>65,07; 67,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,3; 66,01</t>
+          <t>64,65; 66,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KP10in_T-Edad-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -97,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -110,6 +112,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -489,7 +494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por adulto/a (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN percibido por adulto/a (escala) (tasa de respuesta: 49,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -546,147 +551,162 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>65,71</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>65,37</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>65,56</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>65.710862208324</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>65.37208981787832</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>65.55814795525937</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>63,79; 67,83</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>63,01; 67,4</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>64,1; 67,19</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>63.78981379017642</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>63.01341164322068</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>64.09740083296745</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>67.82770596207425</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>67.39660528980592</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>67.18647369741625</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>12-15</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>64,44</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>66,82</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>65,54</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>62,63; 66,14</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>65,07; 68,34</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>64,39; 66,76</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>64.43849462761229</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>66.81823427420414</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>65.54256559569235</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>64,93</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>66,28</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>65,55</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>62.62898099836234</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>65.06518245079492</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>64.38586196204659</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>63,64; 66,39</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>65,07; 67,66</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>64,65; 66,49</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>66.14059775156453</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>68.33711230869415</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>66.76369584064865</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>64.92732094460014</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>66.28067204261059</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>65.54846297643974</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>63.64034898981852</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>65.06789259723863</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>64.65044445765709</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>66.38548833554718</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>67.65564031366436</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>66.48919769510343</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -695,9 +715,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A4:A6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
